--- a/ig/TEST-SUPPLEMENT/CodeSystem-ObservationMethod-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-ObservationMethod-supplement-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="305">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/ObservationMethod-supplement-fr</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/observationMethod-supplement-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -126,784 +126,787 @@
     <t>1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>222</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>239</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>264</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>275</t>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
+    <t>0004</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>0006</t>
+  </si>
+  <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
+    <t>0012</t>
+  </si>
+  <si>
+    <t>0013</t>
+  </si>
+  <si>
+    <t>0014</t>
+  </si>
+  <si>
+    <t>0015</t>
+  </si>
+  <si>
+    <t>0016</t>
+  </si>
+  <si>
+    <t>0017</t>
+  </si>
+  <si>
+    <t>0018</t>
+  </si>
+  <si>
+    <t>0019</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>0021</t>
+  </si>
+  <si>
+    <t>0022</t>
+  </si>
+  <si>
+    <t>0023</t>
+  </si>
+  <si>
+    <t>0024</t>
+  </si>
+  <si>
+    <t>0025</t>
+  </si>
+  <si>
+    <t>0026</t>
+  </si>
+  <si>
+    <t>0027</t>
+  </si>
+  <si>
+    <t>0030</t>
+  </si>
+  <si>
+    <t>0031</t>
+  </si>
+  <si>
+    <t>0032</t>
+  </si>
+  <si>
+    <t>0033</t>
+  </si>
+  <si>
+    <t>0034</t>
+  </si>
+  <si>
+    <t>0037</t>
+  </si>
+  <si>
+    <t>0038</t>
+  </si>
+  <si>
+    <t>0039</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>0041</t>
+  </si>
+  <si>
+    <t>0042</t>
+  </si>
+  <si>
+    <t>0043</t>
+  </si>
+  <si>
+    <t>0044</t>
+  </si>
+  <si>
+    <t>0045</t>
+  </si>
+  <si>
+    <t>0046</t>
+  </si>
+  <si>
+    <t>0047</t>
+  </si>
+  <si>
+    <t>0048</t>
+  </si>
+  <si>
+    <t>0049</t>
+  </si>
+  <si>
+    <t>0050</t>
+  </si>
+  <si>
+    <t>0051</t>
+  </si>
+  <si>
+    <t>0052</t>
+  </si>
+  <si>
+    <t>0053</t>
+  </si>
+  <si>
+    <t>0054</t>
+  </si>
+  <si>
+    <t>0061</t>
+  </si>
+  <si>
+    <t>0062</t>
+  </si>
+  <si>
+    <t>0063</t>
+  </si>
+  <si>
+    <t>0064</t>
+  </si>
+  <si>
+    <t>0065</t>
+  </si>
+  <si>
+    <t>0066</t>
+  </si>
+  <si>
+    <t>0067</t>
+  </si>
+  <si>
+    <t>0068</t>
+  </si>
+  <si>
+    <t>0069</t>
+  </si>
+  <si>
+    <t>0070</t>
+  </si>
+  <si>
+    <t>0071</t>
+  </si>
+  <si>
+    <t>0072</t>
+  </si>
+  <si>
+    <t>0073</t>
+  </si>
+  <si>
+    <t>0074</t>
+  </si>
+  <si>
+    <t>0075</t>
+  </si>
+  <si>
+    <t>0076</t>
+  </si>
+  <si>
+    <t>0077</t>
+  </si>
+  <si>
+    <t>0078</t>
+  </si>
+  <si>
+    <t>0079</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>0081</t>
+  </si>
+  <si>
+    <t>0082</t>
+  </si>
+  <si>
+    <t>0083</t>
+  </si>
+  <si>
+    <t>0084</t>
+  </si>
+  <si>
+    <t>0085</t>
+  </si>
+  <si>
+    <t>0086</t>
+  </si>
+  <si>
+    <t>0087</t>
+  </si>
+  <si>
+    <t>0088</t>
+  </si>
+  <si>
+    <t>0089</t>
+  </si>
+  <si>
+    <t>0090</t>
+  </si>
+  <si>
+    <t>0091</t>
+  </si>
+  <si>
+    <t>0092</t>
+  </si>
+  <si>
+    <t>0093</t>
+  </si>
+  <si>
+    <t>0094</t>
+  </si>
+  <si>
+    <t>0095</t>
+  </si>
+  <si>
+    <t>0096</t>
+  </si>
+  <si>
+    <t>0097</t>
+  </si>
+  <si>
+    <t>0098</t>
+  </si>
+  <si>
+    <t>0099</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>0103</t>
+  </si>
+  <si>
+    <t>0104</t>
+  </si>
+  <si>
+    <t>0105</t>
+  </si>
+  <si>
+    <t>0106</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>0108</t>
+  </si>
+  <si>
+    <t>0109</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>0111</t>
+  </si>
+  <si>
+    <t>0112</t>
+  </si>
+  <si>
+    <t>0113</t>
+  </si>
+  <si>
+    <t>0114</t>
+  </si>
+  <si>
+    <t>0115</t>
+  </si>
+  <si>
+    <t>0116</t>
+  </si>
+  <si>
+    <t>0117</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>0122</t>
+  </si>
+  <si>
+    <t>0123</t>
+  </si>
+  <si>
+    <t>0127</t>
+  </si>
+  <si>
+    <t>0128</t>
+  </si>
+  <si>
+    <t>0129</t>
+  </si>
+  <si>
+    <t>0130</t>
+  </si>
+  <si>
+    <t>0131</t>
+  </si>
+  <si>
+    <t>0132</t>
+  </si>
+  <si>
+    <t>0134</t>
+  </si>
+  <si>
+    <t>0135</t>
+  </si>
+  <si>
+    <t>0138</t>
+  </si>
+  <si>
+    <t>0139</t>
+  </si>
+  <si>
+    <t>0140</t>
+  </si>
+  <si>
+    <t>0141</t>
+  </si>
+  <si>
+    <t>0142</t>
+  </si>
+  <si>
+    <t>0143</t>
+  </si>
+  <si>
+    <t>0144</t>
+  </si>
+  <si>
+    <t>0145</t>
+  </si>
+  <si>
+    <t>0146</t>
+  </si>
+  <si>
+    <t>0147</t>
+  </si>
+  <si>
+    <t>0148</t>
+  </si>
+  <si>
+    <t>0149</t>
+  </si>
+  <si>
+    <t>0150</t>
+  </si>
+  <si>
+    <t>0151</t>
+  </si>
+  <si>
+    <t>0152</t>
+  </si>
+  <si>
+    <t>0153</t>
+  </si>
+  <si>
+    <t>0154</t>
+  </si>
+  <si>
+    <t>0155</t>
+  </si>
+  <si>
+    <t>0156</t>
+  </si>
+  <si>
+    <t>0157</t>
+  </si>
+  <si>
+    <t>0158</t>
+  </si>
+  <si>
+    <t>0159</t>
+  </si>
+  <si>
+    <t>0160</t>
+  </si>
+  <si>
+    <t>0161</t>
+  </si>
+  <si>
+    <t>0162</t>
+  </si>
+  <si>
+    <t>0163</t>
+  </si>
+  <si>
+    <t>0164</t>
+  </si>
+  <si>
+    <t>0165</t>
+  </si>
+  <si>
+    <t>0166</t>
+  </si>
+  <si>
+    <t>0167</t>
+  </si>
+  <si>
+    <t>0168</t>
+  </si>
+  <si>
+    <t>0169</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>0171</t>
+  </si>
+  <si>
+    <t>0172</t>
+  </si>
+  <si>
+    <t>0173</t>
+  </si>
+  <si>
+    <t>0174</t>
+  </si>
+  <si>
+    <t>0175</t>
+  </si>
+  <si>
+    <t>0176</t>
+  </si>
+  <si>
+    <t>0177</t>
+  </si>
+  <si>
+    <t>0178</t>
+  </si>
+  <si>
+    <t>0179</t>
+  </si>
+  <si>
+    <t>0180</t>
+  </si>
+  <si>
+    <t>0181</t>
+  </si>
+  <si>
+    <t>0182</t>
+  </si>
+  <si>
+    <t>0183</t>
+  </si>
+  <si>
+    <t>0184</t>
+  </si>
+  <si>
+    <t>0185</t>
+  </si>
+  <si>
+    <t>0186</t>
+  </si>
+  <si>
+    <t>0187</t>
+  </si>
+  <si>
+    <t>0188</t>
+  </si>
+  <si>
+    <t>0189</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>0191</t>
+  </si>
+  <si>
+    <t>0192</t>
+  </si>
+  <si>
+    <t>0193</t>
+  </si>
+  <si>
+    <t>0194</t>
+  </si>
+  <si>
+    <t>0195</t>
+  </si>
+  <si>
+    <t>0196</t>
+  </si>
+  <si>
+    <t>0197</t>
+  </si>
+  <si>
+    <t>0198</t>
+  </si>
+  <si>
+    <t>0199</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>0201</t>
+  </si>
+  <si>
+    <t>0202</t>
+  </si>
+  <si>
+    <t>0203</t>
+  </si>
+  <si>
+    <t>0204</t>
+  </si>
+  <si>
+    <t>0205</t>
+  </si>
+  <si>
+    <t>0206</t>
+  </si>
+  <si>
+    <t>0207</t>
+  </si>
+  <si>
+    <t>0208</t>
+  </si>
+  <si>
+    <t>0209</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>0211</t>
+  </si>
+  <si>
+    <t>0212</t>
+  </si>
+  <si>
+    <t>0213</t>
+  </si>
+  <si>
+    <t>0214</t>
+  </si>
+  <si>
+    <t>0215</t>
+  </si>
+  <si>
+    <t>0216</t>
+  </si>
+  <si>
+    <t>0217</t>
+  </si>
+  <si>
+    <t>0218</t>
+  </si>
+  <si>
+    <t>0219</t>
+  </si>
+  <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>0221</t>
+  </si>
+  <si>
+    <t>0222</t>
+  </si>
+  <si>
+    <t>0223</t>
+  </si>
+  <si>
+    <t>0224</t>
+  </si>
+  <si>
+    <t>0225</t>
+  </si>
+  <si>
+    <t>0226</t>
+  </si>
+  <si>
+    <t>0227</t>
+  </si>
+  <si>
+    <t>0228</t>
+  </si>
+  <si>
+    <t>0229</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>0231</t>
+  </si>
+  <si>
+    <t>0232</t>
+  </si>
+  <si>
+    <t>0233</t>
+  </si>
+  <si>
+    <t>0234</t>
+  </si>
+  <si>
+    <t>0235</t>
+  </si>
+  <si>
+    <t>0236</t>
+  </si>
+  <si>
+    <t>0237</t>
+  </si>
+  <si>
+    <t>0238</t>
+  </si>
+  <si>
+    <t>0239</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>0241</t>
+  </si>
+  <si>
+    <t>0242</t>
+  </si>
+  <si>
+    <t>0243</t>
+  </si>
+  <si>
+    <t>0244</t>
+  </si>
+  <si>
+    <t>0245</t>
+  </si>
+  <si>
+    <t>0246</t>
+  </si>
+  <si>
+    <t>0247</t>
+  </si>
+  <si>
+    <t>0248</t>
+  </si>
+  <si>
+    <t>0249</t>
+  </si>
+  <si>
+    <t>0250</t>
+  </si>
+  <si>
+    <t>0251</t>
+  </si>
+  <si>
+    <t>0252</t>
+  </si>
+  <si>
+    <t>0253</t>
+  </si>
+  <si>
+    <t>0254</t>
+  </si>
+  <si>
+    <t>0255</t>
+  </si>
+  <si>
+    <t>0256</t>
+  </si>
+  <si>
+    <t>0257</t>
+  </si>
+  <si>
+    <t>0258</t>
+  </si>
+  <si>
+    <t>0259</t>
+  </si>
+  <si>
+    <t>0261</t>
+  </si>
+  <si>
+    <t>0262</t>
+  </si>
+  <si>
+    <t>0263</t>
+  </si>
+  <si>
+    <t>0264</t>
+  </si>
+  <si>
+    <t>0265</t>
+  </si>
+  <si>
+    <t>0266</t>
+  </si>
+  <si>
+    <t>0267</t>
+  </si>
+  <si>
+    <t>0268</t>
+  </si>
+  <si>
+    <t>0269</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>0271</t>
+  </si>
+  <si>
+    <t>0272</t>
+  </si>
+  <si>
+    <t>0273</t>
+  </si>
+  <si>
+    <t>0274</t>
+  </si>
+  <si>
+    <t>0275</t>
   </si>
   <si>
     <t>275a</t>
   </si>
   <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>280</t>
+    <t>0276</t>
+  </si>
+  <si>
+    <t>0277</t>
+  </si>
+  <si>
+    <t>0278</t>
+  </si>
+  <si>
+    <t>0279</t>
+  </si>
+  <si>
+    <t>0280</t>
   </si>
   <si>
     <t>ALGM</t>
@@ -1244,7 +1247,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1254,7 +1257,7 @@
         <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1264,7 +1267,7 @@
         <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1274,7 +1277,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1284,7 +1287,7 @@
         <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1294,7 +1297,7 @@
         <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1304,7 +1307,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1314,7 +1317,7 @@
         <v>36</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1324,7 +1327,7 @@
         <v>36</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1334,7 +1337,7 @@
         <v>36</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1344,7 +1347,7 @@
         <v>36</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1354,7 +1357,7 @@
         <v>36</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1364,7 +1367,7 @@
         <v>36</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1374,7 +1377,7 @@
         <v>36</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -1384,7 +1387,7 @@
         <v>36</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1394,7 +1397,7 @@
         <v>36</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1404,7 +1407,7 @@
         <v>36</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1414,7 +1417,7 @@
         <v>36</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1424,7 +1427,7 @@
         <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1434,7 +1437,7 @@
         <v>36</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1444,7 +1447,7 @@
         <v>36</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1454,7 +1457,7 @@
         <v>36</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1464,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -1474,7 +1477,7 @@
         <v>36</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1484,7 +1487,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1494,7 +1497,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1504,7 +1507,7 @@
         <v>36</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1514,7 +1517,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1524,7 +1527,7 @@
         <v>36</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1534,7 +1537,7 @@
         <v>36</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1544,7 +1547,7 @@
         <v>36</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1554,7 +1557,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1564,7 +1567,7 @@
         <v>36</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1574,7 +1577,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1584,7 +1587,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1594,7 +1597,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1604,7 +1607,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1614,7 +1617,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1624,7 +1627,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -1634,7 +1637,7 @@
         <v>36</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1644,7 +1647,7 @@
         <v>36</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1654,7 +1657,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1664,7 +1667,7 @@
         <v>36</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -1674,7 +1677,7 @@
         <v>36</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -1684,7 +1687,7 @@
         <v>36</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -1694,7 +1697,7 @@
         <v>36</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -1704,7 +1707,7 @@
         <v>36</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -1714,7 +1717,7 @@
         <v>36</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -1724,7 +1727,7 @@
         <v>36</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -1734,7 +1737,7 @@
         <v>36</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -1744,7 +1747,7 @@
         <v>36</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -1754,7 +1757,7 @@
         <v>36</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -1764,7 +1767,7 @@
         <v>36</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -1774,7 +1777,7 @@
         <v>36</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1784,7 +1787,7 @@
         <v>36</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -1794,7 +1797,7 @@
         <v>36</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -1804,7 +1807,7 @@
         <v>36</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -1814,7 +1817,7 @@
         <v>36</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -1824,7 +1827,7 @@
         <v>36</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -1834,7 +1837,7 @@
         <v>36</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -1844,7 +1847,7 @@
         <v>36</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -1854,7 +1857,7 @@
         <v>36</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1864,7 +1867,7 @@
         <v>36</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -1874,7 +1877,7 @@
         <v>36</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -1884,7 +1887,7 @@
         <v>36</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -1894,7 +1897,7 @@
         <v>36</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1904,7 +1907,7 @@
         <v>36</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1914,7 +1917,7 @@
         <v>36</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -1924,7 +1927,7 @@
         <v>36</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -1934,7 +1937,7 @@
         <v>36</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -1944,7 +1947,7 @@
         <v>36</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -1954,7 +1957,7 @@
         <v>36</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -1964,7 +1967,7 @@
         <v>36</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -1974,7 +1977,7 @@
         <v>36</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -1984,7 +1987,7 @@
         <v>36</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -1994,7 +1997,7 @@
         <v>36</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -2004,7 +2007,7 @@
         <v>36</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -2014,7 +2017,7 @@
         <v>36</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -2024,7 +2027,7 @@
         <v>36</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -2034,7 +2037,7 @@
         <v>36</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -2044,7 +2047,7 @@
         <v>36</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -2054,7 +2057,7 @@
         <v>36</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -2064,7 +2067,7 @@
         <v>36</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -2074,7 +2077,7 @@
         <v>36</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -2084,7 +2087,7 @@
         <v>36</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -2094,7 +2097,7 @@
         <v>36</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -2104,7 +2107,7 @@
         <v>36</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -2114,7 +2117,7 @@
         <v>36</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -2124,7 +2127,7 @@
         <v>36</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -2134,7 +2137,7 @@
         <v>36</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -2144,7 +2147,7 @@
         <v>36</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -2154,7 +2157,7 @@
         <v>36</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -2164,7 +2167,7 @@
         <v>36</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -2174,7 +2177,7 @@
         <v>36</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -2184,7 +2187,7 @@
         <v>36</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -2194,7 +2197,7 @@
         <v>36</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -2204,7 +2207,7 @@
         <v>36</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -2214,7 +2217,7 @@
         <v>36</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -2224,7 +2227,7 @@
         <v>36</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -2234,7 +2237,7 @@
         <v>36</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -2244,7 +2247,7 @@
         <v>36</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -2254,7 +2257,7 @@
         <v>36</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -2264,7 +2267,7 @@
         <v>36</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -2274,7 +2277,7 @@
         <v>36</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -2284,7 +2287,7 @@
         <v>36</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -2294,7 +2297,7 @@
         <v>36</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -2304,7 +2307,7 @@
         <v>36</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -2314,7 +2317,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -2324,7 +2327,7 @@
         <v>36</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -2334,7 +2337,7 @@
         <v>36</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -2344,7 +2347,7 @@
         <v>36</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -2354,7 +2357,7 @@
         <v>36</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -2364,7 +2367,7 @@
         <v>36</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -2374,7 +2377,7 @@
         <v>36</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -2384,7 +2387,7 @@
         <v>36</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -2394,7 +2397,7 @@
         <v>36</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -2404,7 +2407,7 @@
         <v>36</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -2414,7 +2417,7 @@
         <v>36</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -2424,7 +2427,7 @@
         <v>36</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -2434,7 +2437,7 @@
         <v>36</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -2444,7 +2447,7 @@
         <v>36</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -2454,7 +2457,7 @@
         <v>36</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -2464,7 +2467,7 @@
         <v>36</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -2474,7 +2477,7 @@
         <v>36</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -2484,7 +2487,7 @@
         <v>36</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -2494,7 +2497,7 @@
         <v>36</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -2504,7 +2507,7 @@
         <v>36</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -2514,7 +2517,7 @@
         <v>36</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -2524,7 +2527,7 @@
         <v>36</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -2534,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -2544,7 +2547,7 @@
         <v>36</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -2554,7 +2557,7 @@
         <v>36</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -2564,7 +2567,7 @@
         <v>36</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -2574,7 +2577,7 @@
         <v>36</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -2584,7 +2587,7 @@
         <v>36</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -2594,7 +2597,7 @@
         <v>36</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -2604,7 +2607,7 @@
         <v>36</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -2614,7 +2617,7 @@
         <v>36</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -2624,7 +2627,7 @@
         <v>36</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -2634,7 +2637,7 @@
         <v>36</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -2644,7 +2647,7 @@
         <v>36</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -2654,7 +2657,7 @@
         <v>36</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -2664,7 +2667,7 @@
         <v>36</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -2674,7 +2677,7 @@
         <v>36</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -2684,7 +2687,7 @@
         <v>36</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -2694,7 +2697,7 @@
         <v>36</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -2704,7 +2707,7 @@
         <v>36</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -2714,7 +2717,7 @@
         <v>36</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -2724,7 +2727,7 @@
         <v>36</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -2734,7 +2737,7 @@
         <v>36</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -2744,7 +2747,7 @@
         <v>36</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -2754,7 +2757,7 @@
         <v>36</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -2764,7 +2767,7 @@
         <v>36</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -2774,7 +2777,7 @@
         <v>36</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -2784,7 +2787,7 @@
         <v>36</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -2794,7 +2797,7 @@
         <v>36</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -2804,7 +2807,7 @@
         <v>36</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -2814,7 +2817,7 @@
         <v>36</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -2824,7 +2827,7 @@
         <v>36</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -2834,7 +2837,7 @@
         <v>36</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -2844,7 +2847,7 @@
         <v>36</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -2854,7 +2857,7 @@
         <v>36</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -2864,7 +2867,7 @@
         <v>36</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -2874,7 +2877,7 @@
         <v>36</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -2884,7 +2887,7 @@
         <v>36</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -2894,7 +2897,7 @@
         <v>36</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -2904,7 +2907,7 @@
         <v>36</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -2914,7 +2917,7 @@
         <v>36</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -2924,7 +2927,7 @@
         <v>36</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -2934,7 +2937,7 @@
         <v>36</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -2944,7 +2947,7 @@
         <v>36</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -2954,7 +2957,7 @@
         <v>36</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -2964,7 +2967,7 @@
         <v>36</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -2974,7 +2977,7 @@
         <v>36</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -2984,7 +2987,7 @@
         <v>36</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -2994,7 +2997,7 @@
         <v>36</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -3004,7 +3007,7 @@
         <v>36</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -3014,7 +3017,7 @@
         <v>36</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -3024,7 +3027,7 @@
         <v>36</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -3034,7 +3037,7 @@
         <v>36</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -3044,7 +3047,7 @@
         <v>36</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -3054,7 +3057,7 @@
         <v>36</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -3064,7 +3067,7 @@
         <v>36</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -3074,7 +3077,7 @@
         <v>36</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -3084,7 +3087,7 @@
         <v>36</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -3094,7 +3097,7 @@
         <v>36</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -3104,7 +3107,7 @@
         <v>36</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -3114,7 +3117,7 @@
         <v>36</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -3124,7 +3127,7 @@
         <v>36</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -3134,7 +3137,7 @@
         <v>36</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -3144,7 +3147,7 @@
         <v>36</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -3154,7 +3157,7 @@
         <v>36</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -3164,7 +3167,7 @@
         <v>36</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -3174,7 +3177,7 @@
         <v>36</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -3184,7 +3187,7 @@
         <v>36</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -3194,7 +3197,7 @@
         <v>36</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -3204,7 +3207,7 @@
         <v>36</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -3214,7 +3217,7 @@
         <v>36</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -3224,7 +3227,7 @@
         <v>36</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -3234,7 +3237,7 @@
         <v>36</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -3244,7 +3247,7 @@
         <v>36</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -3254,7 +3257,7 @@
         <v>36</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -3264,7 +3267,7 @@
         <v>36</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -3274,7 +3277,7 @@
         <v>36</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -3284,7 +3287,7 @@
         <v>36</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -3294,7 +3297,7 @@
         <v>36</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -3304,7 +3307,7 @@
         <v>36</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -3314,7 +3317,7 @@
         <v>36</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -3324,7 +3327,7 @@
         <v>36</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -3334,7 +3337,7 @@
         <v>36</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -3344,7 +3347,7 @@
         <v>36</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -3354,7 +3357,7 @@
         <v>36</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -3364,7 +3367,7 @@
         <v>36</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -3374,7 +3377,7 @@
         <v>36</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -3384,7 +3387,7 @@
         <v>36</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -3394,7 +3397,7 @@
         <v>36</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -3404,7 +3407,7 @@
         <v>36</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -3414,7 +3417,7 @@
         <v>36</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -3424,7 +3427,7 @@
         <v>36</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -3434,7 +3437,7 @@
         <v>36</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -3444,7 +3447,7 @@
         <v>36</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -3454,7 +3457,7 @@
         <v>36</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
@@ -3464,7 +3467,7 @@
         <v>36</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
@@ -3474,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
@@ -3484,7 +3487,7 @@
         <v>36</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
@@ -3494,7 +3497,7 @@
         <v>36</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
@@ -3504,7 +3507,7 @@
         <v>36</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
@@ -3514,7 +3517,7 @@
         <v>36</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
@@ -3524,7 +3527,7 @@
         <v>36</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
@@ -3534,7 +3537,7 @@
         <v>36</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
@@ -3544,7 +3547,7 @@
         <v>36</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
@@ -3554,7 +3557,7 @@
         <v>36</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
@@ -3564,7 +3567,7 @@
         <v>36</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
@@ -3574,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
@@ -3584,7 +3587,7 @@
         <v>36</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
@@ -3594,7 +3597,7 @@
         <v>36</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
@@ -3604,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
@@ -3614,7 +3617,7 @@
         <v>36</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
@@ -3624,7 +3627,7 @@
         <v>36</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
@@ -3634,7 +3637,7 @@
         <v>36</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
@@ -3644,7 +3647,7 @@
         <v>36</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
@@ -3654,7 +3657,7 @@
         <v>36</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -3664,7 +3667,7 @@
         <v>36</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
@@ -3674,7 +3677,7 @@
         <v>36</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
@@ -3684,7 +3687,7 @@
         <v>36</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
@@ -3694,7 +3697,7 @@
         <v>36</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -3704,7 +3707,7 @@
         <v>36</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
@@ -3714,7 +3717,7 @@
         <v>36</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -3724,7 +3727,7 @@
         <v>36</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
@@ -3734,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
@@ -3744,7 +3747,7 @@
         <v>36</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
@@ -3754,7 +3757,7 @@
         <v>36</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
@@ -3764,7 +3767,7 @@
         <v>36</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -3774,7 +3777,7 @@
         <v>36</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
@@ -3784,7 +3787,7 @@
         <v>36</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -3794,7 +3797,7 @@
         <v>36</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
@@ -3804,7 +3807,7 @@
         <v>36</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
@@ -3814,7 +3817,7 @@
         <v>36</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
@@ -3824,7 +3827,7 @@
         <v>36</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
@@ -3834,7 +3837,7 @@
         <v>36</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
@@ -3844,7 +3847,7 @@
         <v>36</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
@@ -3854,7 +3857,7 @@
         <v>36</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
@@ -3864,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
@@ -3874,7 +3877,7 @@
         <v>36</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
@@ -3884,7 +3887,7 @@
         <v>36</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
@@ -3894,7 +3897,7 @@
         <v>36</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
@@ -3904,7 +3907,7 @@
         <v>36</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
@@ -3914,7 +3917,7 @@
         <v>36</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>

--- a/ig/TEST-SUPPLEMENT/CodeSystem-ObservationMethod-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-ObservationMethod-supplement-fr.xlsx
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Traduction Francaise</t>
+    <t>Traduction Française</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -891,7 +891,7 @@
     <t>0275</t>
   </si>
   <si>
-    <t>275a</t>
+    <t>0275a</t>
   </si>
   <si>
     <t>0276</t>
